--- a/GUA/Waste/A1_Outputs/A-O_Demand_COMPLETED.xlsx
+++ b/GUA/Waste/A1_Outputs/A-O_Demand_COMPLETED.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
   <si>
     <t>Demand/Share</t>
   </si>
@@ -43,22 +43,64 @@
     <t>Demand</t>
   </si>
   <si>
-    <t>E5_TSWTSW</t>
-  </si>
-  <si>
-    <t>E5_TWWTWW</t>
+    <t>E5TSWTSW</t>
+  </si>
+  <si>
+    <t>E5TSWLANDFILL_ELEC</t>
+  </si>
+  <si>
+    <t>E5TSWIND_SW</t>
+  </si>
+  <si>
+    <t>E5TSWCO2_CH4_BURN</t>
+  </si>
+  <si>
+    <t>E5TSWCOMPOST_DOM</t>
+  </si>
+  <si>
+    <t>E5TSWCOMPOST_COFFEE</t>
+  </si>
+  <si>
+    <t>E5WWDWW_DC</t>
+  </si>
+  <si>
+    <t>E5WWDWW_N</t>
+  </si>
+  <si>
+    <t>E5WWIWW</t>
   </si>
   <si>
     <t>Demand Total solid waste Total solid waste</t>
   </si>
   <si>
-    <t>Demand Total waste water Total waste water</t>
+    <t>Demand Total solid waste Methane recovery in landfill to generate electricity</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Industrial solid waste</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Carbon dioxide from burning methane</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Domestic compost</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Agroindustrial compost</t>
+  </si>
+  <si>
+    <t>Demand Waste water Domestic wastewater (degradable organic component)</t>
+  </si>
+  <si>
+    <t>Demand Waste water Domestic wastewater (nitrogen)</t>
+  </si>
+  <si>
+    <t>Demand Waste water Industrial waste water</t>
   </si>
   <si>
     <t>not needed</t>
   </si>
   <si>
-    <t>Otro</t>
+    <t>User defined</t>
   </si>
 </sst>
 </file>
@@ -416,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO3"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:41">
@@ -552,118 +594,121 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4.4067</v>
+        <v>2.8971</v>
       </c>
       <c r="J2">
-        <v>4.588</v>
+        <v>3.0177</v>
       </c>
       <c r="K2">
-        <v>4.7693</v>
+        <v>3.1582</v>
       </c>
       <c r="L2">
-        <v>4.9506</v>
+        <v>3.3022</v>
       </c>
       <c r="M2">
-        <v>5.1319</v>
+        <v>3.4495</v>
       </c>
       <c r="N2">
-        <v>5.3269</v>
+        <v>3.5806</v>
       </c>
       <c r="O2">
-        <v>5.5293</v>
+        <v>3.7167</v>
       </c>
       <c r="P2">
-        <v>5.7394</v>
+        <v>3.8579</v>
       </c>
       <c r="Q2">
-        <v>5.9575</v>
+        <v>4.0044</v>
       </c>
       <c r="R2">
-        <v>6.1839</v>
+        <v>4.1566</v>
       </c>
       <c r="S2">
-        <v>6.4189</v>
+        <v>4.3147</v>
       </c>
       <c r="T2">
-        <v>6.6628</v>
+        <v>4.4786</v>
       </c>
       <c r="U2">
-        <v>6.916</v>
+        <v>4.6488</v>
       </c>
       <c r="V2">
-        <v>7.1788</v>
+        <v>4.8255</v>
       </c>
       <c r="W2">
-        <v>7.4516</v>
+        <v>5.0088</v>
       </c>
       <c r="X2">
-        <v>7.7347</v>
+        <v>5.1991</v>
       </c>
       <c r="Y2">
-        <v>8.028700000000001</v>
+        <v>5.3967</v>
       </c>
       <c r="Z2">
-        <v>8.3337</v>
+        <v>5.6017</v>
       </c>
       <c r="AA2">
-        <v>8.650399999999999</v>
+        <v>5.8147</v>
       </c>
       <c r="AB2">
-        <v>8.979100000000001</v>
+        <v>6.0356</v>
       </c>
       <c r="AC2">
-        <v>9.320399999999999</v>
+        <v>6.2649</v>
       </c>
       <c r="AD2">
-        <v>9.6745</v>
+        <v>6.503</v>
       </c>
       <c r="AE2">
-        <v>10.0422</v>
+        <v>6.7501</v>
       </c>
       <c r="AF2">
-        <v>10.4238</v>
+        <v>7.0066</v>
       </c>
       <c r="AG2">
-        <v>10.8199</v>
+        <v>7.2729</v>
       </c>
       <c r="AH2">
-        <v>11.231</v>
+        <v>7.5492</v>
       </c>
       <c r="AI2">
-        <v>11.6578</v>
+        <v>7.8361</v>
       </c>
       <c r="AJ2">
-        <v>12.1008</v>
+        <v>8.133900000000001</v>
       </c>
       <c r="AK2">
-        <v>12.5606</v>
+        <v>8.4429</v>
       </c>
       <c r="AL2">
-        <v>13.0379</v>
+        <v>8.7638</v>
       </c>
       <c r="AM2">
-        <v>13.5334</v>
+        <v>9.0968</v>
       </c>
       <c r="AN2">
-        <v>14.0476</v>
+        <v>9.442500000000001</v>
       </c>
       <c r="AO2">
-        <v>14.5814</v>
+        <v>9.801299999999999</v>
       </c>
     </row>
     <row r="3" spans="1:41">
@@ -674,378 +719,999 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0.0844</v>
+      </c>
+      <c r="J6">
+        <v>0.0861</v>
+      </c>
+      <c r="K6">
+        <v>0.0887</v>
+      </c>
+      <c r="L6">
+        <v>0.0912</v>
+      </c>
+      <c r="M6">
+        <v>0.0936</v>
+      </c>
+      <c r="N6">
+        <v>0.0936</v>
+      </c>
+      <c r="O6">
+        <v>0.0936</v>
+      </c>
+      <c r="P6">
+        <v>0.0936</v>
+      </c>
+      <c r="Q6">
+        <v>0.0936</v>
+      </c>
+      <c r="R6">
+        <v>0.0936</v>
+      </c>
+      <c r="S6">
+        <v>0.0936</v>
+      </c>
+      <c r="T6">
+        <v>0.0936</v>
+      </c>
+      <c r="U6">
+        <v>0.0936</v>
+      </c>
+      <c r="V6">
+        <v>0.0936</v>
+      </c>
+      <c r="W6">
+        <v>0.0936</v>
+      </c>
+      <c r="X6">
+        <v>0.0936</v>
+      </c>
+      <c r="Y6">
+        <v>0.0936</v>
+      </c>
+      <c r="Z6">
+        <v>0.0936</v>
+      </c>
+      <c r="AA6">
+        <v>0.0936</v>
+      </c>
+      <c r="AB6">
+        <v>0.0936</v>
+      </c>
+      <c r="AC6">
+        <v>0.0936</v>
+      </c>
+      <c r="AD6">
+        <v>0.0936</v>
+      </c>
+      <c r="AE6">
+        <v>0.0936</v>
+      </c>
+      <c r="AF6">
+        <v>0.0936</v>
+      </c>
+      <c r="AG6">
+        <v>0.0936</v>
+      </c>
+      <c r="AH6">
+        <v>0.0936</v>
+      </c>
+      <c r="AI6">
+        <v>0.0936</v>
+      </c>
+      <c r="AJ6">
+        <v>0.0936</v>
+      </c>
+      <c r="AK6">
+        <v>0.0936</v>
+      </c>
+      <c r="AL6">
+        <v>0.0936</v>
+      </c>
+      <c r="AM6">
+        <v>0.0936</v>
+      </c>
+      <c r="AN6">
+        <v>0.0936</v>
+      </c>
+      <c r="AO6">
+        <v>0.0936</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>1.7655</v>
-      </c>
-      <c r="J3">
-        <v>1.8326</v>
-      </c>
-      <c r="K3">
-        <v>1.9022</v>
-      </c>
-      <c r="L3">
-        <v>1.9745</v>
-      </c>
-      <c r="M3">
-        <v>2.0495</v>
-      </c>
-      <c r="N3">
-        <v>2.1274</v>
-      </c>
-      <c r="O3">
-        <v>2.2082</v>
-      </c>
-      <c r="P3">
-        <v>2.2921</v>
-      </c>
-      <c r="Q3">
-        <v>2.3792</v>
-      </c>
-      <c r="R3">
-        <v>2.4697</v>
-      </c>
-      <c r="S3">
-        <v>2.5635</v>
-      </c>
-      <c r="T3">
-        <v>2.6609</v>
-      </c>
-      <c r="U3">
-        <v>2.762</v>
-      </c>
-      <c r="V3">
-        <v>2.867</v>
-      </c>
-      <c r="W3">
-        <v>2.9759</v>
-      </c>
-      <c r="X3">
-        <v>3.089</v>
-      </c>
-      <c r="Y3">
-        <v>3.2064</v>
-      </c>
-      <c r="Z3">
-        <v>3.3282</v>
-      </c>
-      <c r="AA3">
-        <v>3.4547</v>
-      </c>
-      <c r="AB3">
-        <v>3.586</v>
-      </c>
-      <c r="AC3">
-        <v>3.7223</v>
-      </c>
-      <c r="AD3">
-        <v>3.8637</v>
-      </c>
-      <c r="AE3">
-        <v>4.0105</v>
-      </c>
-      <c r="AF3">
-        <v>4.1629</v>
-      </c>
-      <c r="AG3">
-        <v>4.3211</v>
-      </c>
-      <c r="AH3">
-        <v>4.4853</v>
-      </c>
-      <c r="AI3">
-        <v>4.6558</v>
-      </c>
-      <c r="AJ3">
-        <v>4.8327</v>
-      </c>
-      <c r="AK3">
-        <v>5.0163</v>
-      </c>
-      <c r="AL3">
-        <v>5.207</v>
-      </c>
-      <c r="AM3">
-        <v>5.4048</v>
-      </c>
-      <c r="AN3">
-        <v>5.6102</v>
-      </c>
-      <c r="AO3">
-        <v>5.8234</v>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.3668</v>
+      </c>
+      <c r="J7">
+        <v>0.3179</v>
+      </c>
+      <c r="K7">
+        <v>0.316</v>
+      </c>
+      <c r="L7">
+        <v>0.3141</v>
+      </c>
+      <c r="M7">
+        <v>0.3122</v>
+      </c>
+      <c r="N7">
+        <v>0.3122</v>
+      </c>
+      <c r="O7">
+        <v>0.3122</v>
+      </c>
+      <c r="P7">
+        <v>0.3122</v>
+      </c>
+      <c r="Q7">
+        <v>0.3122</v>
+      </c>
+      <c r="R7">
+        <v>0.3122</v>
+      </c>
+      <c r="S7">
+        <v>0.3122</v>
+      </c>
+      <c r="T7">
+        <v>0.3122</v>
+      </c>
+      <c r="U7">
+        <v>0.3122</v>
+      </c>
+      <c r="V7">
+        <v>0.3122</v>
+      </c>
+      <c r="W7">
+        <v>0.3122</v>
+      </c>
+      <c r="X7">
+        <v>0.3122</v>
+      </c>
+      <c r="Y7">
+        <v>0.3122</v>
+      </c>
+      <c r="Z7">
+        <v>0.3122</v>
+      </c>
+      <c r="AA7">
+        <v>0.3122</v>
+      </c>
+      <c r="AB7">
+        <v>0.3122</v>
+      </c>
+      <c r="AC7">
+        <v>0.3122</v>
+      </c>
+      <c r="AD7">
+        <v>0.3122</v>
+      </c>
+      <c r="AE7">
+        <v>0.3122</v>
+      </c>
+      <c r="AF7">
+        <v>0.3122</v>
+      </c>
+      <c r="AG7">
+        <v>0.3122</v>
+      </c>
+      <c r="AH7">
+        <v>0.3122</v>
+      </c>
+      <c r="AI7">
+        <v>0.3122</v>
+      </c>
+      <c r="AJ7">
+        <v>0.3122</v>
+      </c>
+      <c r="AK7">
+        <v>0.3122</v>
+      </c>
+      <c r="AL7">
+        <v>0.3122</v>
+      </c>
+      <c r="AM7">
+        <v>0.3122</v>
+      </c>
+      <c r="AN7">
+        <v>0.3122</v>
+      </c>
+      <c r="AO7">
+        <v>0.3122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>11.6499</v>
+      </c>
+      <c r="J8">
+        <v>12.0903</v>
+      </c>
+      <c r="K8">
+        <v>12.2817</v>
+      </c>
+      <c r="L8">
+        <v>12.471</v>
+      </c>
+      <c r="M8">
+        <v>12.6578</v>
+      </c>
+      <c r="N8">
+        <v>13.1388</v>
+      </c>
+      <c r="O8">
+        <v>13.6381</v>
+      </c>
+      <c r="P8">
+        <v>14.1563</v>
+      </c>
+      <c r="Q8">
+        <v>14.6943</v>
+      </c>
+      <c r="R8">
+        <v>15.2526</v>
+      </c>
+      <c r="S8">
+        <v>15.8322</v>
+      </c>
+      <c r="T8">
+        <v>16.4339</v>
+      </c>
+      <c r="U8">
+        <v>17.0584</v>
+      </c>
+      <c r="V8">
+        <v>17.7066</v>
+      </c>
+      <c r="W8">
+        <v>18.3794</v>
+      </c>
+      <c r="X8">
+        <v>19.0778</v>
+      </c>
+      <c r="Y8">
+        <v>19.8028</v>
+      </c>
+      <c r="Z8">
+        <v>20.5553</v>
+      </c>
+      <c r="AA8">
+        <v>21.3364</v>
+      </c>
+      <c r="AB8">
+        <v>22.1472</v>
+      </c>
+      <c r="AC8">
+        <v>22.9888</v>
+      </c>
+      <c r="AD8">
+        <v>23.8624</v>
+      </c>
+      <c r="AE8">
+        <v>24.7691</v>
+      </c>
+      <c r="AF8">
+        <v>25.7103</v>
+      </c>
+      <c r="AG8">
+        <v>26.6873</v>
+      </c>
+      <c r="AH8">
+        <v>27.7015</v>
+      </c>
+      <c r="AI8">
+        <v>28.7541</v>
+      </c>
+      <c r="AJ8">
+        <v>29.8468</v>
+      </c>
+      <c r="AK8">
+        <v>30.981</v>
+      </c>
+      <c r="AL8">
+        <v>32.1582</v>
+      </c>
+      <c r="AM8">
+        <v>33.3802</v>
+      </c>
+      <c r="AN8">
+        <v>34.6487</v>
+      </c>
+      <c r="AO8">
+        <v>35.9653</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>102.7812</v>
+      </c>
+      <c r="J9">
+        <v>101.9675</v>
+      </c>
+      <c r="K9">
+        <v>97.6878</v>
+      </c>
+      <c r="L9">
+        <v>91.2393</v>
+      </c>
+      <c r="M9">
+        <v>103.2446</v>
+      </c>
+      <c r="N9">
+        <v>107.1679</v>
+      </c>
+      <c r="O9">
+        <v>111.2403</v>
+      </c>
+      <c r="P9">
+        <v>115.4674</v>
+      </c>
+      <c r="Q9">
+        <v>119.8552</v>
+      </c>
+      <c r="R9">
+        <v>124.4097</v>
+      </c>
+      <c r="S9">
+        <v>129.1372</v>
+      </c>
+      <c r="T9">
+        <v>134.0444</v>
+      </c>
+      <c r="U9">
+        <v>139.1381</v>
+      </c>
+      <c r="V9">
+        <v>144.4254</v>
+      </c>
+      <c r="W9">
+        <v>149.9135</v>
+      </c>
+      <c r="X9">
+        <v>155.6103</v>
+      </c>
+      <c r="Y9">
+        <v>161.5234</v>
+      </c>
+      <c r="Z9">
+        <v>167.6613</v>
+      </c>
+      <c r="AA9">
+        <v>174.0325</v>
+      </c>
+      <c r="AB9">
+        <v>180.6457</v>
+      </c>
+      <c r="AC9">
+        <v>187.5102</v>
+      </c>
+      <c r="AD9">
+        <v>194.6356</v>
+      </c>
+      <c r="AE9">
+        <v>202.0318</v>
+      </c>
+      <c r="AF9">
+        <v>209.709</v>
+      </c>
+      <c r="AG9">
+        <v>217.6779</v>
+      </c>
+      <c r="AH9">
+        <v>225.9497</v>
+      </c>
+      <c r="AI9">
+        <v>234.5358</v>
+      </c>
+      <c r="AJ9">
+        <v>243.4481</v>
+      </c>
+      <c r="AK9">
+        <v>252.6992</v>
+      </c>
+      <c r="AL9">
+        <v>262.3017</v>
+      </c>
+      <c r="AM9">
+        <v>272.2692</v>
+      </c>
+      <c r="AN9">
+        <v>282.6154</v>
+      </c>
+      <c r="AO9">
+        <v>293.3548</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>20.5574</v>
+      </c>
+      <c r="J10">
+        <v>10.6769</v>
+      </c>
+      <c r="K10">
+        <v>10.6136</v>
+      </c>
+      <c r="L10">
+        <v>10.5504</v>
+      </c>
+      <c r="M10">
+        <v>10.4872</v>
+      </c>
+      <c r="N10">
+        <v>10.8857</v>
+      </c>
+      <c r="O10">
+        <v>11.2994</v>
+      </c>
+      <c r="P10">
+        <v>11.7287</v>
+      </c>
+      <c r="Q10">
+        <v>12.1744</v>
+      </c>
+      <c r="R10">
+        <v>12.6371</v>
+      </c>
+      <c r="S10">
+        <v>13.1173</v>
+      </c>
+      <c r="T10">
+        <v>13.6157</v>
+      </c>
+      <c r="U10">
+        <v>14.1331</v>
+      </c>
+      <c r="V10">
+        <v>14.6702</v>
+      </c>
+      <c r="W10">
+        <v>15.2277</v>
+      </c>
+      <c r="X10">
+        <v>15.8063</v>
+      </c>
+      <c r="Y10">
+        <v>16.4069</v>
+      </c>
+      <c r="Z10">
+        <v>17.0304</v>
+      </c>
+      <c r="AA10">
+        <v>17.6776</v>
+      </c>
+      <c r="AB10">
+        <v>18.3493</v>
+      </c>
+      <c r="AC10">
+        <v>19.0466</v>
+      </c>
+      <c r="AD10">
+        <v>19.7704</v>
+      </c>
+      <c r="AE10">
+        <v>20.5216</v>
+      </c>
+      <c r="AF10">
+        <v>21.3014</v>
+      </c>
+      <c r="AG10">
+        <v>22.1109</v>
+      </c>
+      <c r="AH10">
+        <v>22.9511</v>
+      </c>
+      <c r="AI10">
+        <v>23.8233</v>
+      </c>
+      <c r="AJ10">
+        <v>24.7285</v>
+      </c>
+      <c r="AK10">
+        <v>25.6682</v>
+      </c>
+      <c r="AL10">
+        <v>26.6436</v>
+      </c>
+      <c r="AM10">
+        <v>27.6561</v>
+      </c>
+      <c r="AN10">
+        <v>28.707</v>
+      </c>
+      <c r="AO10">
+        <v>29.7979</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
-    <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
-    <xsd:import namespace="081a93ea-d517-42a5-a2b7-457060aa7471"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="081a93ea-d517-42a5-a2b7-457060aa7471" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{234FCEF6-60EB-4CFA-B3FF-023A016E7CAF}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8B4E541-F5E3-459B-BF9A-8B8B9B707554}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED6C4BB-C098-4B66-BE68-08806C50E2DF}"/>
 </file>